--- a/AAII_Financials/Quarterly/CRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>CRM</t>
   </si>
@@ -656,520 +656,532 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
         <v>46142</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43039</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42947</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42766</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11345000</v>
+      </c>
+      <c r="E8" s="3">
         <v>11133000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11201000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10259000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10236000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9829000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9993000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9444000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9325000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9133000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9287000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8720000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8603000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8247000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8384000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7837000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7720000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7411000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7326000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6863000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6340000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5963000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5817000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5419000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5151000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4865000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4851000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4513000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3997000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3737000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3603000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3392000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3281000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3006000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2865000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2701000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2577000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2397000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2294000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2144800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2649000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2570000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2508000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2255000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2242000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2265000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2217000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2105000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2159000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2162000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2148000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2155000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2113000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2125000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2100000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2088000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2127000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2045000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2014000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1844000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1613000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1555000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1479000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1394000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1311000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1254000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1220000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1134000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>967000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>914000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>946000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>889000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>849000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>767000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>738000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>714000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>670000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>651000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>626000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>585500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8696000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8563000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8693000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8004000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7994000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7564000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7776000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7339000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7166000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6971000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7139000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6565000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6490000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6122000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6284000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5749000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5593000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5366000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5312000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5019000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4727000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4408000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4338000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4025000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3840000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3611000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3631000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3379000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3030000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2823000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2657000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2503000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2432000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2239000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2127000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1987000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1907000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1746000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1668000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1559300</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1212,130 +1224,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1687000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1627000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1619000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1433000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1481000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1460000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1420000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1356000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1349000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1368000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1275000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1204000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1220000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1207000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1128000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1280000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1329000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1318000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1291000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1203000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1020000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>951000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>939000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>902000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>898000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>859000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>831000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>774000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>607000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>554000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>518000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>481000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>463000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>424000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>396000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>394000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>387000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>376000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>344200</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>311500</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1456,112 +1472,115 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-2519000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-478000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-525000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>99000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>202000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>273000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>136000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-29000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>208000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>127000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>78000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>852000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1198000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>68000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>42000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>11000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>11000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>20000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>14000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>166000</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>5000</v>
-      </c>
-      <c r="AK14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>10</v>
@@ -1578,130 +1597,136 @@
       <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E15" s="3">
         <v>741000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1587000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>851000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>817000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>843000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>877000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>814000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>907000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>879000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>953000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>862000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>890000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1254000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>223000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>224000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>232000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>237000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>236000</v>
       </c>
       <c r="V15" s="3">
         <v>236000</v>
       </c>
       <c r="W15" s="3">
+        <v>236000</v>
+      </c>
+      <c r="X15" s="3">
         <v>135000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>120000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>115000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>114000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>118000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>112000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>110000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>109000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>65000</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>68000</v>
       </c>
       <c r="AG15" s="3">
         <v>68000</v>
       </c>
       <c r="AH15" s="3">
-        <v>67000</v>
+        <v>68000</v>
       </c>
       <c r="AI15" s="3">
         <v>67000</v>
       </c>
       <c r="AJ15" s="3">
+        <v>67000</v>
+      </c>
+      <c r="AK15" s="3">
         <v>30000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>30300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>30400</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>31400</v>
       </c>
       <c r="AN15" s="3">
         <v>31400</v>
       </c>
       <c r="AO15" s="3">
+        <v>31400</v>
+      </c>
+      <c r="AP15" s="3">
         <v>31600</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1741,252 +1766,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8920000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8706000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9046000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7811000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7900000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7851000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7875000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7495000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7443000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7416000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7492000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7164000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7078000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7124000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8397000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7445000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7569000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7402000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7508000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6836000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6028000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5623000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5624000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5195000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4973000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5005000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4887000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4448000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3939000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3527000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3466000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3300000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3166000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2815000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2654000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2546000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2493000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2393000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2317900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2142300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2425000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2427000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2155000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2448000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2336000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1978000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2118000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1949000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1882000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1717000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1795000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1556000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1525000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1123000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>392000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>151000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-182000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>27000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>312000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>340000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>193000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>224000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>178000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-140000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-36000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>65000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>58000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>210000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>137000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>92000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>115000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>191000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>211000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>155000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>84000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>4000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-23900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2029,323 +2061,330 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-24000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-13000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>11000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>15000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-43000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>22000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>75000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>370000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-128000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-120000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>109000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>158000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>106000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>36000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>56000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>344000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>554000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>297000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>283000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1051000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>686000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>212000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>62000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>30000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>140000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>307000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>143000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>76000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>155000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>228000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>32000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>12000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>1000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>8000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>24800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3375000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3192000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3755000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3288000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3138000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2815000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3038000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2755000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2767000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2521000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2378000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2546000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2535000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2432000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1128000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1491000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1164000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>951000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>805000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1334000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1585000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1322000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1345000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1945000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1513000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>730000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>659000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>703000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>655000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>954000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>553000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>424000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>522000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>600000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>431000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>355000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>277000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>197000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>181600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>178700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>473000</v>
+      </c>
+      <c r="E22" s="3">
         <v>317000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>147000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>67000</v>
       </c>
       <c r="G22" s="3">
         <v>67000</v>
       </c>
       <c r="H22" s="3">
+        <v>67000</v>
+      </c>
+      <c r="I22" s="3">
         <v>68000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>96000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>67000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>68000</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>99000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>70000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>75000</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>63000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>75000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>76000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>74000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>71000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>72000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>40000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>33000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>51000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>25000</v>
       </c>
       <c r="AA22" s="3">
         <v>25000</v>
@@ -2354,293 +2393,302 @@
         <v>25000</v>
       </c>
       <c r="AC22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>30000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>31000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>34000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>35000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>41000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>40000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>34000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>22000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>21000</v>
-      </c>
-      <c r="AM22" s="3">
-        <v>22000</v>
       </c>
       <c r="AN22" s="3">
         <v>22000</v>
       </c>
       <c r="AO22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AP22" s="3">
         <v>24300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4552000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2721000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2628000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2512000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2406000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1974000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1988000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1746000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1837000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1867000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1645000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1487000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1492000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>326000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>475000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>181000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-29000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-197000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>299000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>826000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>604000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>425000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1250000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>839000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>47000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>64000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>164000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>482000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>239000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>128000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>231000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>385000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>221000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>146000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>63000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-23500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1026000</v>
+      </c>
+      <c r="E24" s="3">
         <v>614000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>685000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>426000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>519000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>433000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>280000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>219000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>408000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>334000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>199000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>263000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>225000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>127000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>131000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>265000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>113000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-57000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-169000</v>
       </c>
       <c r="V24" s="3">
         <v>-169000</v>
       </c>
       <c r="W24" s="3">
+        <v>-169000</v>
+      </c>
+      <c r="X24" s="3">
         <v>291000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>135000</v>
       </c>
       <c r="Y24" s="3">
         <v>135000</v>
       </c>
       <c r="Z24" s="3">
+        <v>135000</v>
+      </c>
+      <c r="AA24" s="3">
         <v>169000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-52000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>238000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>173000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>73000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>90000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-166000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>23000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-68000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>41000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-111000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>39000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>17000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-11000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>28000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2761,252 +2809,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3526000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2107000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1943000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2086000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1887000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1541000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1708000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1527000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1429000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1533000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1446000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1224000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1267000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>199000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-98000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>210000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>68000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>28000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-28000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>468000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>535000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>469000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>290000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1081000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2625000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>99000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-242000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-109000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>91000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>392000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>405000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>105000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>299000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>344000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>332000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>107000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>46000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-51400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3526000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2107000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1943000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2086000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1887000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1541000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1708000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1527000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1429000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1533000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1446000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1224000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1267000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>199000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-98000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>210000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>68000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>28000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-28000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>468000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>535000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>469000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>290000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1081000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2625000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>99000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-242000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-109000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>91000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>392000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>405000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>105000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>299000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>344000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>332000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>107000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>46000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-51400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3127,8 +3184,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3177,17 +3237,17 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>10</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>10</v>
@@ -3195,11 +3255,11 @@
       <c r="X29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-23000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
@@ -3207,11 +3267,11 @@
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-6000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>10</v>
@@ -3219,11 +3279,11 @@
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-43000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>10</v>
@@ -3231,11 +3291,11 @@
       <c r="AJ29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-126000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>10</v>
@@ -3249,8 +3309,11 @@
       <c r="AP29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3371,8 +3434,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3493,252 +3559,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E32" s="3">
         <v>24000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>13000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-11000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-15000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>43000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-22000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-75000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-370000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>128000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>120000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>55000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-109000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-158000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-106000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-36000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-56000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-344000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-554000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-297000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-283000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1051000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-686000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-212000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-62000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-140000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-307000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-143000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-76000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-228000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-24800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3526000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2107000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1943000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2086000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1887000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1541000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1708000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1527000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1429000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1533000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1446000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1224000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1267000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>199000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-98000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>210000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>68000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>28000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-28000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>468000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>535000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>469000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>267000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1081000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2625000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>99000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-248000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-109000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>91000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>392000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>362000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>105000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>299000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>344000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>206000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>107000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>46000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-51400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3859,257 +3934,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3526000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2107000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1943000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2086000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1887000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1541000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1708000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1527000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1429000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1533000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1446000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1224000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1267000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>199000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-98000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>210000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>68000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>28000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-28000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>468000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>535000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>469000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>267000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1081000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2625000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>99000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-248000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-109000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>91000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>392000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>362000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>105000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>299000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>344000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>206000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>107000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>46000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-51400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
         <v>46142</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43039</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42947</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42766</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4152,8 +4236,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4196,374 +4281,384 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8310000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8935000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7327000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8978000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10365000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10928000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8848000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7997000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7682000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9958000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8472000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6453000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6772000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9155000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7016000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6076000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6931000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6859000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5464000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4753000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6299000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8544000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6195000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3724000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4052000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5772000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4145000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3868000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3510000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4110000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2669000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2105000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2319000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5922000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2543000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2071800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1949100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2024900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1606500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1145700</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3093000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2902000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2238000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2345000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5007000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6480000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5184000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4760000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4954000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7712000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5722000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5410000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5625000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4822000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5492000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>5842000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>6602000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>6644000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>5073000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4638000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3351000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>6479000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5771000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5768000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5231000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>4030000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3802000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2661000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2532000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2269000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1673000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1345000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1108000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1237000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1978000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1556800</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1552100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1194600</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>602300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>55100</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6320000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5080000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14339000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5474000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5596000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4354000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11945000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4741000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5391000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4273000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11414000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4850000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5400000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4632000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12531000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5824000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6276000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5430000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11193000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5261000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5285000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4340000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8932000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4333000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4393000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3957000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7100000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3386000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3118000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2939000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5712000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2753000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2688000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2464000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4625000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1553000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1606000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1473600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3230800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1307300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4606,8 +4701,8 @@
       <c r="P44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4684,618 +4779,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2074000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2065000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2075000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1835000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1862000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1924000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1971000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1836000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1851000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1865000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1905000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1757000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1781000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1772000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1356000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1467000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1437000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1478000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1120000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1305000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1321000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1081000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>991000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1121000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1170000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>954000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>916000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1111000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>743000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>717000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>629000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>667000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>687000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>528000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>964900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>764500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>704100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>711400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>557100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>493500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22083000</v>
+      </c>
+      <c r="E46" s="3">
         <v>21613000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28222000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21063000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25331000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25866000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>29727000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21425000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21862000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25604000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29074000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20202000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21138000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21981000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>26395000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>19209000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21246000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>20411000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>22850000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15957000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16256000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>20444000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>21889000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14946000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14846000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14713000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15963000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>11026000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9903000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10035000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10683000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6870000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6802000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>10151000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>9584000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5946200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5811300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5404500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5996800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>3001600</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11324000</v>
+      </c>
+      <c r="E47" s="3">
         <v>7772000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7591000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6410000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5085000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4941000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4852000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4845000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5017000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4978000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4848000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4774000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4778000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4633000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7369000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7425000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7491000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7259000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7126000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5854000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5925000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5680000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5666000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5443000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3931000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3146000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3404000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2983000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2800000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2797000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2655000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2378000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2371000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2200000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1941000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>670400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>657700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>639200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>567000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1106300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4829000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5039000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5123000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5096000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5182000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5260000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5393000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5583000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5710000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5761000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6055000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6325000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6451000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6341000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6592000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6418000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6102000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5781000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5695000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5677000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5834000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5555000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5663000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5526000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5513000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5501000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5415000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5515000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5187000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5097000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2051000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1998000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1986000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1950000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1947000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1864900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1866600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1846400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1787500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1756700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>65392000</v>
+      </c>
+      <c r="E49" s="3">
         <v>65941000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>64756000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>55948000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>55107000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>55314000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>55711000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>53212000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>53356000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>53809000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>53898000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>54351000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>54748000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>55221000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>55693000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>56153000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>56640000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>56878000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>56915000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>57423000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>57849000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>30565000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>30432000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>30711000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>30977000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>29754000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>29858000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>30009000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>14924000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>14648000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>14926000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>15078000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>14408000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8429000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>8478800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>8357500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>8431600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>8507900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>8567700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>7888700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5416,8 +5529,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5538,8 +5654,11 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5582,86 +5701,89 @@
       <c r="P52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R52" s="3">
         <v>2800000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2679000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2669000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2693000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2623000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2525000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2794000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2641000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2651000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2510000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2513000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>509000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>486000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>409000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>522000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>577000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>422000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>264000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>256000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>233000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>999400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>651100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>651600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>661000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>675500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>634500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5782,130 +5904,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>109620000</v>
+      </c>
+      <c r="E54" s="3">
         <v>106680000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>112305000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>95144000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>97573000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>98610000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>102928000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>91395000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>92180000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>96180000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>99823000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>91022000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>92447000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>93541000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>98849000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>91884000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>94148000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>93022000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>95209000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>87436000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>88658000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64885000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>66301000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>59136000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57780000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>53623000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>55126000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>49942000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33336000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>33154000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>30737000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>26588000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>25823000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>22963000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>21984000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>17490000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>17418800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>17058900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>17584900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>14387700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5948,8 +6076,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5992,195 +6121,199 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4671000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4444000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4678000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3574000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3427000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3741000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3521000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3163000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3261000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3672000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3119000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3348000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3158000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4901000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6743000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5285000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5446000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4603000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5474000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4231000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4274000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3439000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4355000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3546000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3485000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2916000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3356000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2763000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2271000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2050000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>165000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>160000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>201000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>134000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>146900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>120000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>148300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>128100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>227500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>140500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>678000</v>
+      </c>
+      <c r="E58" s="3">
         <v>795000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4823000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>640000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>750000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>856000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>916000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>663000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>749000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1859000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1889000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1618000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1693000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>990000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>1182000</v>
       </c>
       <c r="R58" s="3">
         <v>1182000</v>
       </c>
       <c r="S58" s="3">
+        <v>1182000</v>
+      </c>
+      <c r="T58" s="3">
         <v>1183000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1002000</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X58" s="3">
         <v>1339000</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>10</v>
@@ -6194,538 +6327,553 @@
       <c r="AB58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD58" s="3">
         <v>53000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>65000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>76000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>178000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>216000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>706000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>708000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>103000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1128000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1272000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1269400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1143200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>121700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18787000</v>
+      </c>
+      <c r="E59" s="3">
         <v>20363000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24317000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14996000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16555000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17799000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20743000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13549000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15291000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16118000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19123000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12628000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14354000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15735000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17966000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11760000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13451000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14294000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16314000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10804000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11780000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11884000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13373000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8688000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9478000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9927000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11436000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7646000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7848000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8260000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10874000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7156000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7560000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7658000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9838600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5824400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>6108500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>6354600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>7657500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>4815500</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26336000</v>
+      </c>
+      <c r="E60" s="3">
         <v>27502000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>37118000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21410000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22532000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24196000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27980000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19375000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21001000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23149000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26631000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19394000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20805000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21626000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>25891000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18227000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>20080000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19899000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21788000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>15035000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17393000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>15323000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>17728000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12234000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12963000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>12843000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>14845000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>10474000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>10195000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>10488000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>11255000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8022000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8469000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7895000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>10067000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7216400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>7526200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>7625900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>7295500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4975500</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>41698000</v>
+      </c>
+      <c r="E61" s="3">
         <v>41753000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12888000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10995000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11059000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11164000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11154000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11515000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11439000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11533000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11673000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12141000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12208000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12924000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9419000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9418000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9416000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9595000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10592000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10591000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10589000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2672000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2673000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2672000</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>2673000</v>
       </c>
       <c r="AB61" s="3">
         <v>2673000</v>
       </c>
       <c r="AC61" s="3">
+        <v>2673000</v>
+      </c>
+      <c r="AD61" s="3">
         <v>3005000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3158000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3309000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3532000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3430000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3685000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3690000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3885000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>695000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1327000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1329900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1392300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2690000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2496200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3208000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3190000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3157000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2718000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2654000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2584000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2621000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1980000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2107000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1815000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1873000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1397000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1352000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1579000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5180000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4888000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4554000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4652000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4698000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4756000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5156000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4323000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4407000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3920000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3704000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3542000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3391000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3031000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2666000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2688000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>447000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>188000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>136000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>123000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>967000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>117200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>111400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>106300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>136500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6846,8 +6994,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6968,8 +7119,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7090,130 +7244,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>71242000</v>
+      </c>
+      <c r="E66" s="3">
         <v>72445000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53163000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35123000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36245000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37944000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41755000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32870000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34547000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36497000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>40177000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32932000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34365000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>36129000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40490000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32533000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34050000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34146000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>37078000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>30382000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>33138000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>22318000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24808000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18826000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19340000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19058000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21241000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16663000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16170000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16708000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>15132000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11895000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12295000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>11903000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>11608000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>8660700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>8967500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>9124400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>10084800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7581600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7256,8 +7416,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7378,8 +7539,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7500,8 +7664,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7622,8 +7789,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7744,130 +7914,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27107000</v>
+      </c>
+      <c r="E72" s="3">
         <v>23954000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22221000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20673000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18987000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17504000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16369000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15049000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13907000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12866000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11721000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10275000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9051000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7784000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7585000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7683000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7473000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7405000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7377000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7405000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6937000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6402000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5933000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5666000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4585000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1960000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1861000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2109000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2218000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2127000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1735000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1373000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1269000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>969000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>635000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-405000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-456400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-474100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-464900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-413500</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7988,8 +8164,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8110,8 +8289,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8232,130 +8414,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38378000</v>
+      </c>
+      <c r="E76" s="3">
         <v>34235000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>59142000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>60021000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>61328000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>60666000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>61173000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>58525000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>57633000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>59683000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>59646000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>58090000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>58082000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>57412000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>58359000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>59351000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>60098000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>58876000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>58131000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>57054000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>55520000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>42567000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>41493000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>40310000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>38440000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>34565000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>33885000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>33279000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17166000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>16446000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15605000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14693000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13528000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11060000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10376000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>8829400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>8451300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7934500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7500100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6806000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8476,257 +8664,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
         <v>46142</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43039</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42947</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42766</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3526000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2107000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1943000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2086000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1887000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1541000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1708000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1527000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1429000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1533000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1446000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1224000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1267000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>199000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-98000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>210000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>68000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>28000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-28000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>468000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>535000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>469000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>267000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1081000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2625000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>99000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-248000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-109000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>91000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>392000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>362000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>105000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>299000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>344000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>206000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>107000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>46000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-51400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-37300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8769,130 +8966,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>437000</v>
+      </c>
+      <c r="E83" s="3">
         <v>448000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>495000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>460000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>453000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>418000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>495000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>394000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>418000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>783000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>510000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>467000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>415000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>394000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1032000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>941000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>907000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>906000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>931000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>963000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>719000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>685000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>869000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>670000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>649000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>658000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>633000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>608000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>457000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>437000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>273000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>256000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>252000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>181000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>188000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>187600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>192300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>185100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>180800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>169300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9013,8 +9214,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9135,8 +9339,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9257,8 +9464,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9379,8 +9589,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9501,130 +9714,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1269000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6701000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5464000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2316000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>740000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6476000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3970000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1983000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>892000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6247000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3403000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1532000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>808000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4491000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2788000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>313000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>334000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3676000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1982000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>404000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>386000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3228000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2174000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>339000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>429000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1859000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1632000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>298000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>436000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1965000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1331000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>143000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>458000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1466000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1051400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>125600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>331000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1230000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>706100</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>154300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9667,130 +9886,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-171000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-145000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-141000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-139000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-135000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-179000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-154000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-204000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-137000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-163000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-147000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-166000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-180000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-243000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-218000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-198000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-203000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-179000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-167000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-166000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-213000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-171000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-149000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-124000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-114000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-323000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-170000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-178000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-159000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-167000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-170000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-122000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-138000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-111000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-128400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-313600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-144000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-140700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9911,8 +10134,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10033,130 +10259,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1197000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2183000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8707000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>519000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1165000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1567000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2936000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-217000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2641000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2651000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-468000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-54000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1152000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>347000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>312000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>533000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-377000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2457000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1459000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-976000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11054000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>94000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2593000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-437000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1465000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>63000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-852000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-726000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-378000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-545000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4661000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>276000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-583900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-135300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-523600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-767700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-497800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-193800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10199,40 +10431,41 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E96" s="3">
         <v>365000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>391000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>395000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>399000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>402000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>383000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>382000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>384000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>388000</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>10</v>
@@ -10243,8 +10476,8 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10321,8 +10554,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10443,8 +10679,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10565,8 +10804,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10687,370 +10929,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-622000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2921000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1588000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4244000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2503000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2920000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-73000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1446000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5802000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2108000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-946000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1765000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2050000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2716000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2221000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1678000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>136000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>201000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>203000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-970000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>8440000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>165000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>176000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>368000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>441000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>209000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>125000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>15000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-183000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>207000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-386000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>182000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>589000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1625000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>19200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>134000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>117000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-49000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>260000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>81800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E101" s="3">
         <v>91000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-110000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-7000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>30000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-32000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>17000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>61000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-23000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-21000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>61000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-23000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-21000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-25000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-15000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-17000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>27000</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>3000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>6000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>12000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-15800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>6100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-7500</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-625000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1608000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1651000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1387000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-563000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2080000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>851000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>315000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2276000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1486000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2019000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-319000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2383000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2139000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>940000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-855000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>72000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1395000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>711000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1546000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2245000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2349000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2471000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-328000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1627000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>277000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>358000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-600000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1441000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>564000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-214000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3603000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3379000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>471600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>122700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-75800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>418400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>460800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>30500</v>
       </c>
     </row>
